--- a/data/qa/prospect_to_cash/customer_order.xlsx
+++ b/data/qa/prospect_to_cash/customer_order.xlsx
@@ -18,13 +18,16 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="0"/>
-  <fonts count="1">
+  <fonts count="2">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
       <color theme="1"/>
       <sz val="11"/>
       <scheme val="minor"/>
+    </font>
+    <font>
+      <b val="1"/>
     </font>
   </fonts>
   <fills count="2">
@@ -35,7 +38,7 @@
       <patternFill patternType="gray125"/>
     </fill>
   </fills>
-  <borders count="1">
+  <borders count="2">
     <border>
       <left/>
       <right/>
@@ -43,12 +46,21 @@
       <bottom/>
       <diagonal/>
     </border>
+    <border>
+      <left style="thin"/>
+      <right style="thin"/>
+      <top style="thin"/>
+      <bottom style="thin"/>
+    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="1">
+  <cellXfs count="2">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="top"/>
+    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -414,126 +426,126 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:X4"/>
+  <dimension ref="A1:X10"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
-      <c r="A1" t="inlineStr">
+      <c r="A1" s="1" t="inlineStr">
         <is>
           <t>qa_id</t>
         </is>
       </c>
-      <c r="B1" t="inlineStr">
+      <c r="B1" s="1" t="inlineStr">
         <is>
           <t>domain</t>
         </is>
       </c>
-      <c r="C1" t="inlineStr">
+      <c r="C1" s="1" t="inlineStr">
         <is>
           <t>process</t>
         </is>
       </c>
-      <c r="D1" t="inlineStr">
+      <c r="D1" s="1" t="inlineStr">
         <is>
           <t>module</t>
         </is>
       </c>
-      <c r="E1" t="inlineStr">
+      <c r="E1" s="1" t="inlineStr">
         <is>
           <t>form</t>
         </is>
       </c>
-      <c r="F1" t="inlineStr">
+      <c r="F1" s="1" t="inlineStr">
         <is>
           <t>field</t>
         </is>
       </c>
-      <c r="G1" t="inlineStr">
+      <c r="G1" s="1" t="inlineStr">
         <is>
           <t>intent</t>
         </is>
       </c>
-      <c r="H1" t="inlineStr">
+      <c r="H1" s="1" t="inlineStr">
         <is>
           <t>sub_intent</t>
         </is>
       </c>
-      <c r="I1" t="inlineStr">
+      <c r="I1" s="1" t="inlineStr">
         <is>
           <t>canonical_question</t>
         </is>
       </c>
-      <c r="J1" t="inlineStr">
+      <c r="J1" s="1" t="inlineStr">
         <is>
           <t>answer</t>
         </is>
       </c>
-      <c r="K1" t="inlineStr">
+      <c r="K1" s="1" t="inlineStr">
         <is>
           <t>keywords</t>
         </is>
       </c>
-      <c r="L1" t="inlineStr">
+      <c r="L1" s="1" t="inlineStr">
         <is>
           <t>synonyms</t>
         </is>
       </c>
-      <c r="M1" t="inlineStr">
+      <c r="M1" s="1" t="inlineStr">
         <is>
           <t>route</t>
         </is>
       </c>
-      <c r="N1" t="inlineStr">
+      <c r="N1" s="1" t="inlineStr">
         <is>
           <t>source_reference</t>
         </is>
       </c>
-      <c r="O1" t="inlineStr">
+      <c r="O1" s="1" t="inlineStr">
         <is>
           <t>source_section</t>
         </is>
       </c>
-      <c r="P1" t="inlineStr">
+      <c r="P1" s="1" t="inlineStr">
         <is>
           <t>version</t>
         </is>
       </c>
-      <c r="Q1" t="inlineStr">
+      <c r="Q1" s="1" t="inlineStr">
         <is>
           <t>site_scope</t>
         </is>
       </c>
-      <c r="R1" t="inlineStr">
+      <c r="R1" s="1" t="inlineStr">
         <is>
           <t>security_scope</t>
         </is>
       </c>
-      <c r="S1" t="inlineStr">
+      <c r="S1" s="1" t="inlineStr">
         <is>
           <t>approval_status</t>
         </is>
       </c>
-      <c r="T1" t="inlineStr">
+      <c r="T1" s="1" t="inlineStr">
         <is>
           <t>approved_by</t>
         </is>
       </c>
-      <c r="U1" t="inlineStr">
+      <c r="U1" s="1" t="inlineStr">
         <is>
           <t>effective_date</t>
         </is>
       </c>
-      <c r="V1" t="inlineStr">
+      <c r="V1" s="1" t="inlineStr">
         <is>
           <t>active</t>
         </is>
       </c>
-      <c r="W1" t="inlineStr">
+      <c r="W1" s="1" t="inlineStr">
         <is>
           <t>last_reviewed_date</t>
         </is>
       </c>
-      <c r="X1" t="inlineStr">
+      <c r="X1" s="1" t="inlineStr">
         <is>
           <t>language</t>
         </is>
@@ -542,7 +554,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>QA-0013</t>
+          <t>KB-0033</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
@@ -552,50 +564,38 @@
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>Customer Order</t>
+          <t>Customer Order Module</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>Order Entry</t>
-        </is>
-      </c>
-      <c r="E2" t="inlineStr">
-        <is>
-          <t>Customer Orders</t>
-        </is>
-      </c>
+          <t>Customer Order Module</t>
+        </is>
+      </c>
+      <c r="E2" t="inlineStr"/>
       <c r="F2" t="inlineStr"/>
       <c r="G2" t="inlineStr">
         <is>
           <t>HELP_GENERIC</t>
         </is>
       </c>
-      <c r="H2" t="inlineStr">
-        <is>
-          <t>definition</t>
-        </is>
-      </c>
+      <c r="H2" t="inlineStr"/>
       <c r="I2" t="inlineStr">
         <is>
-          <t>What is a Customer Order?</t>
+          <t>What information does the Customer Orders form hold and what is its purpose?</t>
         </is>
       </c>
       <c r="J2" t="inlineStr">
         <is>
-          <t>A Customer Order is the confirmed request from a Customer to purchase goods or services, created after a Quotation is accepted. It drives fulfillment, invoicing, and payment.</t>
+          <t>Customer Orders holds the order header, including customer, ship-to, order type and status, dates, terms, shipping and billing defaults, and credit hold information. The order header controls the commercial transaction.</t>
         </is>
       </c>
       <c r="K2" t="inlineStr">
         <is>
-          <t>customer order,sales order</t>
-        </is>
-      </c>
-      <c r="L2" t="inlineStr">
-        <is>
-          <t>sales order,order</t>
-        </is>
-      </c>
+          <t>customer order, Customer Orders form, order header, sales order</t>
+        </is>
+      </c>
+      <c r="L2" t="inlineStr"/>
       <c r="M2" t="inlineStr">
         <is>
           <t>FAST_QA</t>
@@ -603,18 +603,16 @@
       </c>
       <c r="N2" t="inlineStr">
         <is>
-          <t>PTC Training Guide</t>
+          <t>customer_order.md</t>
         </is>
       </c>
       <c r="O2" t="inlineStr">
         <is>
-          <t>4.0</t>
-        </is>
-      </c>
-      <c r="P2" t="inlineStr">
-        <is>
-          <t>1.0</t>
-        </is>
+          <t>Customer Order Module &gt; Purpose and form ownership</t>
+        </is>
+      </c>
+      <c r="P2" t="n">
+        <v>1</v>
       </c>
       <c r="Q2" t="inlineStr"/>
       <c r="R2" t="inlineStr">
@@ -627,10 +625,14 @@
           <t>APPROVED</t>
         </is>
       </c>
-      <c r="T2" t="inlineStr"/>
+      <c r="T2" t="inlineStr">
+        <is>
+          <t>AUTO-DERIVED from knowledge base — pending SME review</t>
+        </is>
+      </c>
       <c r="U2" t="inlineStr">
         <is>
-          <t>2026-01-01</t>
+          <t>2026-09-24</t>
         </is>
       </c>
       <c r="V2" t="b">
@@ -638,7 +640,7 @@
       </c>
       <c r="W2" t="inlineStr">
         <is>
-          <t>2026-01-01</t>
+          <t>2026-09-24</t>
         </is>
       </c>
       <c r="X2" t="inlineStr">
@@ -650,7 +652,7 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>QA-0004</t>
+          <t>KB-0034</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
@@ -660,54 +662,38 @@
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>Customer Order</t>
+          <t>Customer Order Module</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>Order Entry</t>
-        </is>
-      </c>
-      <c r="E3" t="inlineStr">
-        <is>
-          <t>Customer Orders</t>
-        </is>
-      </c>
-      <c r="F3" t="inlineStr">
-        <is>
-          <t>Due Date</t>
-        </is>
-      </c>
+          <t>Customer Order Module</t>
+        </is>
+      </c>
+      <c r="E3" t="inlineStr"/>
+      <c r="F3" t="inlineStr"/>
       <c r="G3" t="inlineStr">
         <is>
-          <t>HELP_FIELD</t>
-        </is>
-      </c>
-      <c r="H3" t="inlineStr">
-        <is>
-          <t>field_definition</t>
-        </is>
-      </c>
+          <t>HELP_PROCESS</t>
+        </is>
+      </c>
+      <c r="H3" t="inlineStr"/>
       <c r="I3" t="inlineStr">
         <is>
-          <t>What is Due Date on a Customer Order?</t>
+          <t>What is the standard order-entry path in the Customer Order module?</t>
         </is>
       </c>
       <c r="J3" t="inlineStr">
         <is>
-          <t>Due Date is the date the customer expects to receive the ordered goods or services. It drives scheduling and shipment planning.</t>
+          <t>The standard order-entry path is to create the header, save it, add lines, check credit and availability, ship, then invoice.</t>
         </is>
       </c>
       <c r="K3" t="inlineStr">
         <is>
-          <t>due date,customer order</t>
-        </is>
-      </c>
-      <c r="L3" t="inlineStr">
-        <is>
-          <t>delivery date,expected date</t>
-        </is>
-      </c>
+          <t>order entry, customer order, sales order, process</t>
+        </is>
+      </c>
+      <c r="L3" t="inlineStr"/>
       <c r="M3" t="inlineStr">
         <is>
           <t>FAST_QA</t>
@@ -715,18 +701,16 @@
       </c>
       <c r="N3" t="inlineStr">
         <is>
-          <t>PTC Training Guide</t>
+          <t>customer_order.md</t>
         </is>
       </c>
       <c r="O3" t="inlineStr">
         <is>
-          <t>4.2</t>
-        </is>
-      </c>
-      <c r="P3" t="inlineStr">
-        <is>
-          <t>1.0</t>
-        </is>
+          <t>Customer Order Module &gt; Purpose and form ownership</t>
+        </is>
+      </c>
+      <c r="P3" t="n">
+        <v>1</v>
       </c>
       <c r="Q3" t="inlineStr"/>
       <c r="R3" t="inlineStr">
@@ -739,10 +723,14 @@
           <t>APPROVED</t>
         </is>
       </c>
-      <c r="T3" t="inlineStr"/>
+      <c r="T3" t="inlineStr">
+        <is>
+          <t>AUTO-DERIVED from knowledge base — pending SME review</t>
+        </is>
+      </c>
       <c r="U3" t="inlineStr">
         <is>
-          <t>2026-01-01</t>
+          <t>2026-09-24</t>
         </is>
       </c>
       <c r="V3" t="b">
@@ -750,7 +738,7 @@
       </c>
       <c r="W3" t="inlineStr">
         <is>
-          <t>2026-01-01</t>
+          <t>2026-09-24</t>
         </is>
       </c>
       <c r="X3" t="inlineStr">
@@ -762,7 +750,7 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>QA-0006</t>
+          <t>KB-0035</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -772,43 +760,35 @@
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>Customer Order</t>
+          <t>Customer Order Module</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>Order Entry</t>
-        </is>
-      </c>
-      <c r="E4" t="inlineStr">
-        <is>
-          <t>Customer Orders</t>
-        </is>
-      </c>
+          <t>Customer Order Module</t>
+        </is>
+      </c>
+      <c r="E4" t="inlineStr"/>
       <c r="F4" t="inlineStr"/>
       <c r="G4" t="inlineStr">
         <is>
           <t>HELP_PROCESS</t>
         </is>
       </c>
-      <c r="H4" t="inlineStr">
-        <is>
-          <t>how_to</t>
-        </is>
-      </c>
+      <c r="H4" t="inlineStr"/>
       <c r="I4" t="inlineStr">
         <is>
-          <t>How do I create a Customer Order?</t>
+          <t>How do I create and review a customer order?</t>
         </is>
       </c>
       <c r="J4" t="inlineStr">
         <is>
-          <t>Open the Customer Orders form, select New, choose the customer, add order lines with item and quantity, then release the order once complete.</t>
+          <t>Search existing orders and customer purchase order references to avoid duplicates. Create a record on Customer Orders, select customer and ship-to, fill required header values, review order details, save the header, add order lines, and review pricing, dates, and availability. Print an Order Verification Report if an acknowledgement is needed.</t>
         </is>
       </c>
       <c r="K4" t="inlineStr">
         <is>
-          <t>create customer order,new order</t>
+          <t>create order, customer order, order review, order verification</t>
         </is>
       </c>
       <c r="L4" t="inlineStr"/>
@@ -819,18 +799,16 @@
       </c>
       <c r="N4" t="inlineStr">
         <is>
-          <t>PTC Training Guide</t>
+          <t>customer_order.md</t>
         </is>
       </c>
       <c r="O4" t="inlineStr">
         <is>
-          <t>4.1</t>
-        </is>
-      </c>
-      <c r="P4" t="inlineStr">
-        <is>
-          <t>1.0</t>
-        </is>
+          <t>Customer Order Module &gt; Create and review an order</t>
+        </is>
+      </c>
+      <c r="P4" t="n">
+        <v>1</v>
       </c>
       <c r="Q4" t="inlineStr"/>
       <c r="R4" t="inlineStr">
@@ -843,10 +821,14 @@
           <t>APPROVED</t>
         </is>
       </c>
-      <c r="T4" t="inlineStr"/>
+      <c r="T4" t="inlineStr">
+        <is>
+          <t>AUTO-DERIVED from knowledge base — pending SME review</t>
+        </is>
+      </c>
       <c r="U4" t="inlineStr">
         <is>
-          <t>2026-01-01</t>
+          <t>2026-09-24</t>
         </is>
       </c>
       <c r="V4" t="b">
@@ -854,10 +836,598 @@
       </c>
       <c r="W4" t="inlineStr">
         <is>
-          <t>2026-01-01</t>
+          <t>2026-09-24</t>
         </is>
       </c>
       <c r="X4" t="inlineStr">
+        <is>
+          <t>en</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>KB-0036</t>
+        </is>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>PROSPECT_TO_CASH</t>
+        </is>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>Customer Order Module</t>
+        </is>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>Customer Order Module</t>
+        </is>
+      </c>
+      <c r="E5" t="inlineStr"/>
+      <c r="F5" t="inlineStr"/>
+      <c r="G5" t="inlineStr">
+        <is>
+          <t>HELP_PROCESS</t>
+        </is>
+      </c>
+      <c r="H5" t="inlineStr"/>
+      <c r="I5" t="inlineStr">
+        <is>
+          <t>What should I review when entering a customer order?</t>
+        </is>
+      </c>
+      <c r="J5" t="inlineStr">
+        <is>
+          <t>Review order type, status, order/requested dates, customer PO, bill-to, ship-to, terms, currency, tax, freight, and salesperson when present. Also review unit price, due date, shipping site, available quantity, credit status, and order totals.</t>
+        </is>
+      </c>
+      <c r="K5" t="inlineStr">
+        <is>
+          <t>order review, customer order, order details, order entry</t>
+        </is>
+      </c>
+      <c r="L5" t="inlineStr"/>
+      <c r="M5" t="inlineStr">
+        <is>
+          <t>FAST_QA</t>
+        </is>
+      </c>
+      <c r="N5" t="inlineStr">
+        <is>
+          <t>customer_order.md</t>
+        </is>
+      </c>
+      <c r="O5" t="inlineStr">
+        <is>
+          <t>Customer Order Module &gt; Create and review an order</t>
+        </is>
+      </c>
+      <c r="P5" t="n">
+        <v>1</v>
+      </c>
+      <c r="Q5" t="inlineStr"/>
+      <c r="R5" t="inlineStr">
+        <is>
+          <t>ALL</t>
+        </is>
+      </c>
+      <c r="S5" t="inlineStr">
+        <is>
+          <t>APPROVED</t>
+        </is>
+      </c>
+      <c r="T5" t="inlineStr">
+        <is>
+          <t>AUTO-DERIVED from knowledge base — pending SME review</t>
+        </is>
+      </c>
+      <c r="U5" t="inlineStr">
+        <is>
+          <t>2026-09-24</t>
+        </is>
+      </c>
+      <c r="V5" t="b">
+        <v>1</v>
+      </c>
+      <c r="W5" t="inlineStr">
+        <is>
+          <t>2026-09-24</t>
+        </is>
+      </c>
+      <c r="X5" t="inlineStr">
+        <is>
+          <t>en</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>KB-0037</t>
+        </is>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>PROSPECT_TO_CASH</t>
+        </is>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>Customer Order Module</t>
+        </is>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>Customer Order Module</t>
+        </is>
+      </c>
+      <c r="E6" t="inlineStr"/>
+      <c r="F6" t="inlineStr"/>
+      <c r="G6" t="inlineStr">
+        <is>
+          <t>HELP_GENERIC</t>
+        </is>
+      </c>
+      <c r="H6" t="inlineStr"/>
+      <c r="I6" t="inlineStr">
+        <is>
+          <t>What is the difference between order and line statuses in the Customer Order module?</t>
+        </is>
+      </c>
+      <c r="J6" t="inlineStr">
+        <is>
+          <t>Order and line statuses are separate. Infor uses Planned and Ordered line states, and a credit check can leave a line Planned or put an order on hold depending on settings.</t>
+        </is>
+      </c>
+      <c r="K6" t="inlineStr">
+        <is>
+          <t>order status, line status, Planned, Ordered, credit hold</t>
+        </is>
+      </c>
+      <c r="L6" t="inlineStr"/>
+      <c r="M6" t="inlineStr">
+        <is>
+          <t>FAST_QA</t>
+        </is>
+      </c>
+      <c r="N6" t="inlineStr">
+        <is>
+          <t>customer_order.md</t>
+        </is>
+      </c>
+      <c r="O6" t="inlineStr">
+        <is>
+          <t>Customer Order Module &gt; Status, holds, and changes</t>
+        </is>
+      </c>
+      <c r="P6" t="n">
+        <v>1</v>
+      </c>
+      <c r="Q6" t="inlineStr"/>
+      <c r="R6" t="inlineStr">
+        <is>
+          <t>ALL</t>
+        </is>
+      </c>
+      <c r="S6" t="inlineStr">
+        <is>
+          <t>APPROVED</t>
+        </is>
+      </c>
+      <c r="T6" t="inlineStr">
+        <is>
+          <t>AUTO-DERIVED from knowledge base — pending SME review</t>
+        </is>
+      </c>
+      <c r="U6" t="inlineStr">
+        <is>
+          <t>2026-09-24</t>
+        </is>
+      </c>
+      <c r="V6" t="b">
+        <v>1</v>
+      </c>
+      <c r="W6" t="inlineStr">
+        <is>
+          <t>2026-09-24</t>
+        </is>
+      </c>
+      <c r="X6" t="inlineStr">
+        <is>
+          <t>en</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>KB-0038</t>
+        </is>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>PROSPECT_TO_CASH</t>
+        </is>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>Customer Order Module</t>
+        </is>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>Customer Order Module</t>
+        </is>
+      </c>
+      <c r="E7" t="inlineStr"/>
+      <c r="F7" t="inlineStr"/>
+      <c r="G7" t="inlineStr">
+        <is>
+          <t>HELP_PROCESS</t>
+        </is>
+      </c>
+      <c r="H7" t="inlineStr"/>
+      <c r="I7" t="inlineStr">
+        <is>
+          <t>What should I check before changing or releasing an order that's on hold?</t>
+        </is>
+      </c>
+      <c r="J7" t="inlineStr">
+        <is>
+          <t>Identify the current status, hold reason, error, line, and local authorization first. For a submitted change, recheck price, dates, tax, allocation, and downstream shipment or invoice history.</t>
+        </is>
+      </c>
+      <c r="K7" t="inlineStr">
+        <is>
+          <t>release order, hold, change order, status, authorization</t>
+        </is>
+      </c>
+      <c r="L7" t="inlineStr"/>
+      <c r="M7" t="inlineStr">
+        <is>
+          <t>FAST_QA</t>
+        </is>
+      </c>
+      <c r="N7" t="inlineStr">
+        <is>
+          <t>customer_order.md</t>
+        </is>
+      </c>
+      <c r="O7" t="inlineStr">
+        <is>
+          <t>Customer Order Module &gt; Status, holds, and changes</t>
+        </is>
+      </c>
+      <c r="P7" t="n">
+        <v>1</v>
+      </c>
+      <c r="Q7" t="inlineStr"/>
+      <c r="R7" t="inlineStr">
+        <is>
+          <t>ALL</t>
+        </is>
+      </c>
+      <c r="S7" t="inlineStr">
+        <is>
+          <t>APPROVED</t>
+        </is>
+      </c>
+      <c r="T7" t="inlineStr">
+        <is>
+          <t>AUTO-DERIVED from knowledge base — pending SME review</t>
+        </is>
+      </c>
+      <c r="U7" t="inlineStr">
+        <is>
+          <t>2026-09-24</t>
+        </is>
+      </c>
+      <c r="V7" t="b">
+        <v>1</v>
+      </c>
+      <c r="W7" t="inlineStr">
+        <is>
+          <t>2026-09-24</t>
+        </is>
+      </c>
+      <c r="X7" t="inlineStr">
+        <is>
+          <t>en</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>KB-0039</t>
+        </is>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>PROSPECT_TO_CASH</t>
+        </is>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>Customer Order Module</t>
+        </is>
+      </c>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>Customer Order Module</t>
+        </is>
+      </c>
+      <c r="E8" t="inlineStr"/>
+      <c r="F8" t="inlineStr"/>
+      <c r="G8" t="inlineStr">
+        <is>
+          <t>HELP_GENERIC</t>
+        </is>
+      </c>
+      <c r="H8" t="inlineStr"/>
+      <c r="I8" t="inlineStr">
+        <is>
+          <t>What are the differences between regular and blanket orders?</t>
+        </is>
+      </c>
+      <c r="J8" t="inlineStr">
+        <is>
+          <t>Regular and blanket orders differ. Blanket orders use blanket lines and releases with separate ship dates.</t>
+        </is>
+      </c>
+      <c r="K8" t="inlineStr">
+        <is>
+          <t>blanket order, regular order, blanket lines, order release</t>
+        </is>
+      </c>
+      <c r="L8" t="inlineStr"/>
+      <c r="M8" t="inlineStr">
+        <is>
+          <t>FAST_QA</t>
+        </is>
+      </c>
+      <c r="N8" t="inlineStr">
+        <is>
+          <t>customer_order.md</t>
+        </is>
+      </c>
+      <c r="O8" t="inlineStr">
+        <is>
+          <t>Customer Order Module &gt; Order types and exceptions</t>
+        </is>
+      </c>
+      <c r="P8" t="n">
+        <v>1</v>
+      </c>
+      <c r="Q8" t="inlineStr"/>
+      <c r="R8" t="inlineStr">
+        <is>
+          <t>ALL</t>
+        </is>
+      </c>
+      <c r="S8" t="inlineStr">
+        <is>
+          <t>APPROVED</t>
+        </is>
+      </c>
+      <c r="T8" t="inlineStr">
+        <is>
+          <t>AUTO-DERIVED from knowledge base — pending SME review</t>
+        </is>
+      </c>
+      <c r="U8" t="inlineStr">
+        <is>
+          <t>2026-09-24</t>
+        </is>
+      </c>
+      <c r="V8" t="b">
+        <v>1</v>
+      </c>
+      <c r="W8" t="inlineStr">
+        <is>
+          <t>2026-09-24</t>
+        </is>
+      </c>
+      <c r="X8" t="inlineStr">
+        <is>
+          <t>en</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>KB-0040</t>
+        </is>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>PROSPECT_TO_CASH</t>
+        </is>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>Customer Order Module</t>
+        </is>
+      </c>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>Customer Order Module</t>
+        </is>
+      </c>
+      <c r="E9" t="inlineStr"/>
+      <c r="F9" t="inlineStr"/>
+      <c r="G9" t="inlineStr">
+        <is>
+          <t>HELP_GENERIC</t>
+        </is>
+      </c>
+      <c r="H9" t="inlineStr"/>
+      <c r="I9" t="inlineStr">
+        <is>
+          <t>What optional features can an order have in the Customer Order module?</t>
+        </is>
+      </c>
+      <c r="J9" t="inlineStr">
+        <is>
+          <t>An order may have multiple shipping sites, drop-ship lines, EDI origin, letter-of-credit requirements, or shipment approval. These are optional or configuration-dependent paths.</t>
+        </is>
+      </c>
+      <c r="K9" t="inlineStr">
+        <is>
+          <t>multi-site, drop ship, EDI order, letter-of-credit, shipment approval</t>
+        </is>
+      </c>
+      <c r="L9" t="inlineStr"/>
+      <c r="M9" t="inlineStr">
+        <is>
+          <t>FAST_QA</t>
+        </is>
+      </c>
+      <c r="N9" t="inlineStr">
+        <is>
+          <t>customer_order.md</t>
+        </is>
+      </c>
+      <c r="O9" t="inlineStr">
+        <is>
+          <t>Customer Order Module &gt; Order types and exceptions</t>
+        </is>
+      </c>
+      <c r="P9" t="n">
+        <v>1</v>
+      </c>
+      <c r="Q9" t="inlineStr"/>
+      <c r="R9" t="inlineStr">
+        <is>
+          <t>ALL</t>
+        </is>
+      </c>
+      <c r="S9" t="inlineStr">
+        <is>
+          <t>APPROVED</t>
+        </is>
+      </c>
+      <c r="T9" t="inlineStr">
+        <is>
+          <t>AUTO-DERIVED from knowledge base — pending SME review</t>
+        </is>
+      </c>
+      <c r="U9" t="inlineStr">
+        <is>
+          <t>2026-09-24</t>
+        </is>
+      </c>
+      <c r="V9" t="b">
+        <v>1</v>
+      </c>
+      <c r="W9" t="inlineStr">
+        <is>
+          <t>2026-09-24</t>
+        </is>
+      </c>
+      <c r="X9" t="inlineStr">
+        <is>
+          <t>en</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>KB-0041</t>
+        </is>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>PROSPECT_TO_CASH</t>
+        </is>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>Customer Order Module</t>
+        </is>
+      </c>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t>Customer Order Module</t>
+        </is>
+      </c>
+      <c r="E10" t="inlineStr"/>
+      <c r="F10" t="inlineStr"/>
+      <c r="G10" t="inlineStr">
+        <is>
+          <t>HELP_PROCESS</t>
+        </is>
+      </c>
+      <c r="H10" t="inlineStr"/>
+      <c r="I10" t="inlineStr">
+        <is>
+          <t>How do I troubleshoot a customer order that cannot progress?</t>
+        </is>
+      </c>
+      <c r="J10" t="inlineStr">
+        <is>
+          <t>Check the exact error and order number; review the current header and line status; verify customer and order credit hold; ensure there are no missing or invalid customer, ship-to, item, quantity, price, due date, site, tax, or terms; check availability and cross-referenced supply; review letter-of-credit and shipment approval settings; and confirm whether the line already shipped or invoiced. The Order Entry Exception Report can help identify processing errors.</t>
+        </is>
+      </c>
+      <c r="K10" t="inlineStr">
+        <is>
+          <t>order won't process, order exception, cannot ship, troubleshoot</t>
+        </is>
+      </c>
+      <c r="L10" t="inlineStr"/>
+      <c r="M10" t="inlineStr">
+        <is>
+          <t>FAST_QA</t>
+        </is>
+      </c>
+      <c r="N10" t="inlineStr">
+        <is>
+          <t>customer_order.md</t>
+        </is>
+      </c>
+      <c r="O10" t="inlineStr">
+        <is>
+          <t>Customer Order Module &gt; Troubleshoot an order that cannot progress</t>
+        </is>
+      </c>
+      <c r="P10" t="n">
+        <v>1</v>
+      </c>
+      <c r="Q10" t="inlineStr"/>
+      <c r="R10" t="inlineStr">
+        <is>
+          <t>ALL</t>
+        </is>
+      </c>
+      <c r="S10" t="inlineStr">
+        <is>
+          <t>APPROVED</t>
+        </is>
+      </c>
+      <c r="T10" t="inlineStr">
+        <is>
+          <t>AUTO-DERIVED from knowledge base — pending SME review</t>
+        </is>
+      </c>
+      <c r="U10" t="inlineStr">
+        <is>
+          <t>2026-09-24</t>
+        </is>
+      </c>
+      <c r="V10" t="b">
+        <v>1</v>
+      </c>
+      <c r="W10" t="inlineStr">
+        <is>
+          <t>2026-09-24</t>
+        </is>
+      </c>
+      <c r="X10" t="inlineStr">
         <is>
           <t>en</t>
         </is>
@@ -874,36 +1444,36 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F4"/>
+  <dimension ref="A1:F28"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
-      <c r="A1" t="inlineStr">
+      <c r="A1" s="1" t="inlineStr">
         <is>
           <t>qa_id</t>
         </is>
       </c>
-      <c r="B1" t="inlineStr">
+      <c r="B1" s="1" t="inlineStr">
         <is>
           <t>variation_id</t>
         </is>
       </c>
-      <c r="C1" t="inlineStr">
+      <c r="C1" s="1" t="inlineStr">
         <is>
           <t>question_variation</t>
         </is>
       </c>
-      <c r="D1" t="inlineStr">
+      <c r="D1" s="1" t="inlineStr">
         <is>
           <t>language</t>
         </is>
       </c>
-      <c r="E1" t="inlineStr">
+      <c r="E1" s="1" t="inlineStr">
         <is>
           <t>source</t>
         </is>
       </c>
-      <c r="F1" t="inlineStr">
+      <c r="F1" s="1" t="inlineStr">
         <is>
           <t>validated</t>
         </is>
@@ -912,7 +1482,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>QA-0013</t>
+          <t>KB-0033</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
@@ -922,7 +1492,7 @@
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>define customer order</t>
+          <t>What does the Customer Orders form do?</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
@@ -932,27 +1502,27 @@
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>manual</t>
+          <t>auto_derived</t>
         </is>
       </c>
       <c r="F2" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>QA-0004</t>
+          <t>KB-0033</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>V1</t>
+          <t>V2</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>what does due date mean</t>
+          <t>What info is stored in the order header?</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
@@ -962,41 +1532,761 @@
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>manual</t>
+          <t>auto_derived</t>
         </is>
       </c>
       <c r="F3" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>QA-0006</t>
+          <t>KB-0033</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
+          <t>V3</t>
+        </is>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>What's the purpose of the Customer Orders form?</t>
+        </is>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>en</t>
+        </is>
+      </c>
+      <c r="E4" t="inlineStr">
+        <is>
+          <t>auto_derived</t>
+        </is>
+      </c>
+      <c r="F4" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>KB-0034</t>
+        </is>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
           <t>V1</t>
         </is>
       </c>
-      <c r="C4" t="inlineStr">
-        <is>
-          <t>steps to create a customer order</t>
-        </is>
-      </c>
-      <c r="D4" t="inlineStr">
-        <is>
-          <t>en</t>
-        </is>
-      </c>
-      <c r="E4" t="inlineStr">
-        <is>
-          <t>manual</t>
-        </is>
-      </c>
-      <c r="F4" t="b">
-        <v>1</v>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>How do I enter a customer order?</t>
+        </is>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>en</t>
+        </is>
+      </c>
+      <c r="E5" t="inlineStr">
+        <is>
+          <t>auto_derived</t>
+        </is>
+      </c>
+      <c r="F5" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>KB-0034</t>
+        </is>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>V2</t>
+        </is>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>What are the steps for order entry?</t>
+        </is>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>en</t>
+        </is>
+      </c>
+      <c r="E6" t="inlineStr">
+        <is>
+          <t>auto_derived</t>
+        </is>
+      </c>
+      <c r="F6" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>KB-0034</t>
+        </is>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>V3</t>
+        </is>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>What's the process for entering a sales order?</t>
+        </is>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>en</t>
+        </is>
+      </c>
+      <c r="E7" t="inlineStr">
+        <is>
+          <t>auto_derived</t>
+        </is>
+      </c>
+      <c r="F7" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>KB-0035</t>
+        </is>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>V1</t>
+        </is>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>What are the steps to create a new customer order?</t>
+        </is>
+      </c>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>en</t>
+        </is>
+      </c>
+      <c r="E8" t="inlineStr">
+        <is>
+          <t>auto_derived</t>
+        </is>
+      </c>
+      <c r="F8" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>KB-0035</t>
+        </is>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>V2</t>
+        </is>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>How can I review and enter a customer order?</t>
+        </is>
+      </c>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>en</t>
+        </is>
+      </c>
+      <c r="E9" t="inlineStr">
+        <is>
+          <t>auto_derived</t>
+        </is>
+      </c>
+      <c r="F9" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>KB-0035</t>
+        </is>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>V3</t>
+        </is>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>What's the process for entering and checking a customer order?</t>
+        </is>
+      </c>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t>en</t>
+        </is>
+      </c>
+      <c r="E10" t="inlineStr">
+        <is>
+          <t>auto_derived</t>
+        </is>
+      </c>
+      <c r="F10" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>KB-0036</t>
+        </is>
+      </c>
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>V1</t>
+        </is>
+      </c>
+      <c r="C11" t="inlineStr">
+        <is>
+          <t>What details do I need to check on a customer order?</t>
+        </is>
+      </c>
+      <c r="D11" t="inlineStr">
+        <is>
+          <t>en</t>
+        </is>
+      </c>
+      <c r="E11" t="inlineStr">
+        <is>
+          <t>auto_derived</t>
+        </is>
+      </c>
+      <c r="F11" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>KB-0036</t>
+        </is>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>V2</t>
+        </is>
+      </c>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t>Which fields should I review when entering an order?</t>
+        </is>
+      </c>
+      <c r="D12" t="inlineStr">
+        <is>
+          <t>en</t>
+        </is>
+      </c>
+      <c r="E12" t="inlineStr">
+        <is>
+          <t>auto_derived</t>
+        </is>
+      </c>
+      <c r="F12" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>KB-0036</t>
+        </is>
+      </c>
+      <c r="B13" t="inlineStr">
+        <is>
+          <t>V3</t>
+        </is>
+      </c>
+      <c r="C13" t="inlineStr">
+        <is>
+          <t>What information should I verify on a new customer order?</t>
+        </is>
+      </c>
+      <c r="D13" t="inlineStr">
+        <is>
+          <t>en</t>
+        </is>
+      </c>
+      <c r="E13" t="inlineStr">
+        <is>
+          <t>auto_derived</t>
+        </is>
+      </c>
+      <c r="F13" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="inlineStr">
+        <is>
+          <t>KB-0037</t>
+        </is>
+      </c>
+      <c r="B14" t="inlineStr">
+        <is>
+          <t>V1</t>
+        </is>
+      </c>
+      <c r="C14" t="inlineStr">
+        <is>
+          <t>How do order and line statuses differ?</t>
+        </is>
+      </c>
+      <c r="D14" t="inlineStr">
+        <is>
+          <t>en</t>
+        </is>
+      </c>
+      <c r="E14" t="inlineStr">
+        <is>
+          <t>auto_derived</t>
+        </is>
+      </c>
+      <c r="F14" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="inlineStr">
+        <is>
+          <t>KB-0037</t>
+        </is>
+      </c>
+      <c r="B15" t="inlineStr">
+        <is>
+          <t>V2</t>
+        </is>
+      </c>
+      <c r="C15" t="inlineStr">
+        <is>
+          <t>What's the difference between order status and line status?</t>
+        </is>
+      </c>
+      <c r="D15" t="inlineStr">
+        <is>
+          <t>en</t>
+        </is>
+      </c>
+      <c r="E15" t="inlineStr">
+        <is>
+          <t>auto_derived</t>
+        </is>
+      </c>
+      <c r="F15" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>KB-0037</t>
+        </is>
+      </c>
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>V3</t>
+        </is>
+      </c>
+      <c r="C16" t="inlineStr">
+        <is>
+          <t>Are order and line statuses the same thing?</t>
+        </is>
+      </c>
+      <c r="D16" t="inlineStr">
+        <is>
+          <t>en</t>
+        </is>
+      </c>
+      <c r="E16" t="inlineStr">
+        <is>
+          <t>auto_derived</t>
+        </is>
+      </c>
+      <c r="F16" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="inlineStr">
+        <is>
+          <t>KB-0038</t>
+        </is>
+      </c>
+      <c r="B17" t="inlineStr">
+        <is>
+          <t>V1</t>
+        </is>
+      </c>
+      <c r="C17" t="inlineStr">
+        <is>
+          <t>What do I need to review before releasing an order?</t>
+        </is>
+      </c>
+      <c r="D17" t="inlineStr">
+        <is>
+          <t>en</t>
+        </is>
+      </c>
+      <c r="E17" t="inlineStr">
+        <is>
+          <t>auto_derived</t>
+        </is>
+      </c>
+      <c r="F17" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="inlineStr">
+        <is>
+          <t>KB-0038</t>
+        </is>
+      </c>
+      <c r="B18" t="inlineStr">
+        <is>
+          <t>V2</t>
+        </is>
+      </c>
+      <c r="C18" t="inlineStr">
+        <is>
+          <t>What should I verify before changing an order on hold?</t>
+        </is>
+      </c>
+      <c r="D18" t="inlineStr">
+        <is>
+          <t>en</t>
+        </is>
+      </c>
+      <c r="E18" t="inlineStr">
+        <is>
+          <t>auto_derived</t>
+        </is>
+      </c>
+      <c r="F18" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="inlineStr">
+        <is>
+          <t>KB-0038</t>
+        </is>
+      </c>
+      <c r="B19" t="inlineStr">
+        <is>
+          <t>V3</t>
+        </is>
+      </c>
+      <c r="C19" t="inlineStr">
+        <is>
+          <t>What steps should I take before releasing or changing a held order?</t>
+        </is>
+      </c>
+      <c r="D19" t="inlineStr">
+        <is>
+          <t>en</t>
+        </is>
+      </c>
+      <c r="E19" t="inlineStr">
+        <is>
+          <t>auto_derived</t>
+        </is>
+      </c>
+      <c r="F19" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="inlineStr">
+        <is>
+          <t>KB-0039</t>
+        </is>
+      </c>
+      <c r="B20" t="inlineStr">
+        <is>
+          <t>V1</t>
+        </is>
+      </c>
+      <c r="C20" t="inlineStr">
+        <is>
+          <t>How is a blanket order different from a regular order?</t>
+        </is>
+      </c>
+      <c r="D20" t="inlineStr">
+        <is>
+          <t>en</t>
+        </is>
+      </c>
+      <c r="E20" t="inlineStr">
+        <is>
+          <t>auto_derived</t>
+        </is>
+      </c>
+      <c r="F20" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="inlineStr">
+        <is>
+          <t>KB-0039</t>
+        </is>
+      </c>
+      <c r="B21" t="inlineStr">
+        <is>
+          <t>V2</t>
+        </is>
+      </c>
+      <c r="C21" t="inlineStr">
+        <is>
+          <t>What makes blanket orders unique compared to standard orders?</t>
+        </is>
+      </c>
+      <c r="D21" t="inlineStr">
+        <is>
+          <t>en</t>
+        </is>
+      </c>
+      <c r="E21" t="inlineStr">
+        <is>
+          <t>auto_derived</t>
+        </is>
+      </c>
+      <c r="F21" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" t="inlineStr">
+        <is>
+          <t>KB-0039</t>
+        </is>
+      </c>
+      <c r="B22" t="inlineStr">
+        <is>
+          <t>V3</t>
+        </is>
+      </c>
+      <c r="C22" t="inlineStr">
+        <is>
+          <t>Can you explain the difference between regular and blanket orders?</t>
+        </is>
+      </c>
+      <c r="D22" t="inlineStr">
+        <is>
+          <t>en</t>
+        </is>
+      </c>
+      <c r="E22" t="inlineStr">
+        <is>
+          <t>auto_derived</t>
+        </is>
+      </c>
+      <c r="F22" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" t="inlineStr">
+        <is>
+          <t>KB-0040</t>
+        </is>
+      </c>
+      <c r="B23" t="inlineStr">
+        <is>
+          <t>V1</t>
+        </is>
+      </c>
+      <c r="C23" t="inlineStr">
+        <is>
+          <t>What extra options can be enabled on an order?</t>
+        </is>
+      </c>
+      <c r="D23" t="inlineStr">
+        <is>
+          <t>en</t>
+        </is>
+      </c>
+      <c r="E23" t="inlineStr">
+        <is>
+          <t>auto_derived</t>
+        </is>
+      </c>
+      <c r="F23" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" t="inlineStr">
+        <is>
+          <t>KB-0040</t>
+        </is>
+      </c>
+      <c r="B24" t="inlineStr">
+        <is>
+          <t>V2</t>
+        </is>
+      </c>
+      <c r="C24" t="inlineStr">
+        <is>
+          <t>Which features might be available for customer orders?</t>
+        </is>
+      </c>
+      <c r="D24" t="inlineStr">
+        <is>
+          <t>en</t>
+        </is>
+      </c>
+      <c r="E24" t="inlineStr">
+        <is>
+          <t>auto_derived</t>
+        </is>
+      </c>
+      <c r="F24" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" t="inlineStr">
+        <is>
+          <t>KB-0040</t>
+        </is>
+      </c>
+      <c r="B25" t="inlineStr">
+        <is>
+          <t>V3</t>
+        </is>
+      </c>
+      <c r="C25" t="inlineStr">
+        <is>
+          <t>Are there any optional settings for orders?</t>
+        </is>
+      </c>
+      <c r="D25" t="inlineStr">
+        <is>
+          <t>en</t>
+        </is>
+      </c>
+      <c r="E25" t="inlineStr">
+        <is>
+          <t>auto_derived</t>
+        </is>
+      </c>
+      <c r="F25" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" t="inlineStr">
+        <is>
+          <t>KB-0041</t>
+        </is>
+      </c>
+      <c r="B26" t="inlineStr">
+        <is>
+          <t>V1</t>
+        </is>
+      </c>
+      <c r="C26" t="inlineStr">
+        <is>
+          <t>What should I check if an order won't process?</t>
+        </is>
+      </c>
+      <c r="D26" t="inlineStr">
+        <is>
+          <t>en</t>
+        </is>
+      </c>
+      <c r="E26" t="inlineStr">
+        <is>
+          <t>auto_derived</t>
+        </is>
+      </c>
+      <c r="F26" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" t="inlineStr">
+        <is>
+          <t>KB-0041</t>
+        </is>
+      </c>
+      <c r="B27" t="inlineStr">
+        <is>
+          <t>V2</t>
+        </is>
+      </c>
+      <c r="C27" t="inlineStr">
+        <is>
+          <t>How can I find out why my order isn't progressing?</t>
+        </is>
+      </c>
+      <c r="D27" t="inlineStr">
+        <is>
+          <t>en</t>
+        </is>
+      </c>
+      <c r="E27" t="inlineStr">
+        <is>
+          <t>auto_derived</t>
+        </is>
+      </c>
+      <c r="F27" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" t="inlineStr">
+        <is>
+          <t>KB-0041</t>
+        </is>
+      </c>
+      <c r="B28" t="inlineStr">
+        <is>
+          <t>V3</t>
+        </is>
+      </c>
+      <c r="C28" t="inlineStr">
+        <is>
+          <t>Steps to diagnose an order that won't release</t>
+        </is>
+      </c>
+      <c r="D28" t="inlineStr">
+        <is>
+          <t>en</t>
+        </is>
+      </c>
+      <c r="E28" t="inlineStr">
+        <is>
+          <t>auto_derived</t>
+        </is>
+      </c>
+      <c r="F28" t="b">
+        <v>0</v>
       </c>
     </row>
   </sheetData>
